--- a/src/ExcelsiorSyncfusion.Tests/LinkTests.UrlOnly.verified.xlsx
+++ b/src/ExcelsiorSyncfusion.Tests/LinkTests.UrlOnly.verified.xlsx
@@ -315,7 +315,7 @@
         <v>9</v>
       </c>
       <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="4" t="s">
         <v>10</v>
       </c>
     </row>
@@ -324,6 +324,7 @@
   <hyperlinks>
     <hyperlink ref="B2" r:id="DeterministicId2" tooltip="https://google.com" display="https://google.com"/>
     <hyperlink ref="C2" r:id="DeterministicId1" tooltip="https://github.com" display="https://github.com"/>
+    <hyperlink ref="F2" r:id="DeterministicId3" tooltip="● https://google.com" display="● https://google.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter scaleWithDoc="1" alignWithMargins="0" differentFirst="0" differentOddEven="0"/>

--- a/src/ExcelsiorSyncfusion.Tests/LinkTests.UrlOnly.verified.xlsx
+++ b/src/ExcelsiorSyncfusion.Tests/LinkTests.UrlOnly.verified.xlsx
@@ -52,9 +52,7 @@
     <r>
       <rPr>
         <b/>
-        <u val="single"/>
-        <sz val="11"/>
-        <color indexed="12"/>
+        <sz val="11"/>
         <rFont val="Calibri"/>
         <charset val="0"/>
       </rPr>
@@ -82,22 +80,20 @@
     <r>
       <rPr>
         <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve">● </t>
+    </r>
+    <r>
+      <rPr>
         <u val="single"/>
         <sz val="11"/>
         <color indexed="12"/>
         <rFont val="Calibri"/>
         <charset val="0"/>
       </rPr>
-      <t xml:space="preserve">● </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="11"/>
-        <color indexed="12"/>
-        <rFont val="Calibri"/>
-        <charset val="0"/>
-      </rPr>
       <t>https://github.com</t>
     </r>
   </si>
@@ -108,9 +104,7 @@
     <r>
       <rPr>
         <b/>
-        <u val="single"/>
-        <sz val="11"/>
-        <color indexed="12"/>
+        <sz val="11"/>
         <rFont val="Calibri"/>
         <charset val="0"/>
       </rPr>
@@ -132,7 +126,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -178,14 +172,6 @@
       <charset val="0"/>
     </font>
     <font>
-      <u val="single"/>
-      <sz val="11"/>
-      <color indexed="12"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <b/>
       <u val="single"/>
       <sz val="11"/>
       <color indexed="12"/>

--- a/src/ExcelsiorSyncfusion.Tests/LinkTests.UrlOnly.verified.xlsx
+++ b/src/ExcelsiorSyncfusion.Tests/LinkTests.UrlOnly.verified.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="DeterministicId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" comment="" localSheetId="0" hidden="1">Sheet1!$A$1:$F$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" comment="" localSheetId="0" hidden="1">Sheet1!$A$1:$C$2</definedName>
   </definedNames>
   <calcPr fullPrecision="1" calcId="125725"/>
 </workbook>
@@ -306,7 +306,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F2"/>
+  <autoFilter ref="A1:C2"/>
   <hyperlinks>
     <hyperlink ref="B2" r:id="DeterministicId2" tooltip="https://google.com" display="https://google.com"/>
     <hyperlink ref="C2" r:id="DeterministicId1" tooltip="https://github.com" display="https://github.com"/>

--- a/src/ExcelsiorSyncfusion.Tests/LinkTests.UrlOnly.verified.xlsx
+++ b/src/ExcelsiorSyncfusion.Tests/LinkTests.UrlOnly.verified.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView/>
+    <workbookView activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="DeterministicId3"/>
+    <sheet name="Evaluation Warning" sheetId="2" r:id="DeterministicId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" comment="" localSheetId="0" hidden="1">Sheet1!$A$1:$C$2</definedName>
@@ -17,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="11" count="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="14" count="14">
   <si>
     <t>Name</t>
   </si>
@@ -119,6 +120,79 @@
         <charset val="0"/>
       </rPr>
       <t>https://google.com</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.syncfusion.com/account/claim-license-key?pl=ZXhjZWw=&amp;vs=MzMuMS40Nw==</t>
+  </si>
+  <si>
+    <r>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="0"/>
+      </rPr>
+      <t>Created with a trial version of Syncfusion Excel library or registered the wrong key in your application. Click</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF0563C1"/>
+        <rFont val="Calibri"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve"> here</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve"> to obtain the valid key.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="0"/>
+      </rPr>
+      <t>Created with a trial version of Syncfusion Excel library or registered the wrong key in your application. Click</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF0563C1"/>
+        <rFont val="Calibri"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve"> here</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve"> to obtain the valid key.</t>
     </r>
   </si>
 </sst>
@@ -126,7 +200,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <fonts count="9">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -175,6 +249,40 @@
       <u val="single"/>
       <sz val="11"/>
       <color indexed="12"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF0563C1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="000563C1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0563C1"/>
       <name val="Calibri"/>
       <charset val="0"/>
     </font>
@@ -202,7 +310,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="27">
+  <cellStyleXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
@@ -238,6 +346,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="20" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="20" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -253,10 +362,100 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1017984</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="0" name="TextBox 36">
+          <a:hlinkClick xmlns:p7="http://schemas.openxmlformats.org/officeDocument/2006/relationships" p7:id="rId1" tooltip="https://www.syncfusion.com/account/claim-license-key?pl=ZXhjZWw=&amp;vs=MzMuMS40Nw=="/>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="18900000">
+          <a:off x="0" y="1"/>
+          <a:ext cx="2076450" cy="1557338"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF">
+            <a:alpha val="10000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-AU" b="1" i="0" sz="1200">
+              <a:solidFill>
+                <a:srgbClr val="FF0000">
+                  <a:alpha val="30000"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:t>Created with a trial version of Syncfusion Excel library or registered the 
+wrong key in your application. Click</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-AU" b="1" i="0" sz="1200">
+              <a:solidFill>
+                <a:srgbClr val="0563C1">
+                  <a:alpha val="30000"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:t> here</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-AU" b="1" i="0" sz="1200">
+              <a:solidFill>
+                <a:srgbClr val="FF0000">
+                  <a:alpha val="30000"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:t> to obtain the valid key.</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-AU" b="1" i="0" sz="1200">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -305,12 +504,49 @@
         <v>10</v>
       </c>
     </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C2"/>
+  <mergeCells count="1">
+    <mergeCell ref="A3:T3"/>
+  </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="DeterministicId2" tooltip="https://google.com" display="https://google.com"/>
-    <hyperlink ref="C2" r:id="DeterministicId1" tooltip="https://github.com" display="https://github.com"/>
-    <hyperlink ref="F2" r:id="DeterministicId3" tooltip="● https://google.com" display="● https://google.com"/>
+    <hyperlink ref="B2" r:id="DeterministicId3" tooltip="https://google.com" display="https://google.com"/>
+    <hyperlink ref="C2" r:id="DeterministicId2" tooltip="https://github.com" display="https://github.com"/>
+    <hyperlink ref="F2" r:id="DeterministicId4" tooltip="● https://google.com" display="● https://google.com"/>
+    <hyperlink ref="A3" r:id="DeterministicId5" tooltip="https://www.syncfusion.com/account/claim-license-key?pl=ZXhjZWw=&amp;vs=MzMuMS40Nw==" display="Created with a trial version of Syncfusion Excel library or registered the wrong key in your application. Click here to obtain the valid key."/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter scaleWithDoc="1" alignWithMargins="0" differentFirst="0" differentOddEven="0"/>
+  <drawing r:id="DeterministicId1"/>
+  <extLst/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FFFF4500"/>
+  </sheetPr>
+  <dimension ref="A10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="10" spans="1:1" ht="25" customHeight="1">
+      <c r="A10" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="xag2jnl27gD1IIru8MwYY0LDEzJ6Otvvkdee3OBMaZGLjmqr4BUk3T5CHfrRRYqWbc1hx5sCzB/FMnaGFkTOvg==" saltValue="BtfTojIS5ppp/ULVoJ82LQ==" spinCount="500" sheet="1" objects="1" scenarios="1" pivotTables="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="A10:S10"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A10" r:id="DeterministicId1" tooltip="https://www.syncfusion.com/account/claim-license-key?pl=ZXhjZWw=&amp;vs=MzMuMS40Nw==" display="Created with a trial version of Syncfusion Excel library or registered the wrong key in your application. Click here to obtain the valid key."/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter scaleWithDoc="1" alignWithMargins="0" differentFirst="0" differentOddEven="0"/>
